--- a/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
+++ b/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Work/Development/mdtu-ddm/mdtu-ddm-gerrit-workspace/mdtu-ddm/general/ddm-architecture/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A9C770-4D25-9741-B108-599B8657515C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D966C3E-2F98-AA4E-8DB0-3BC59D58316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{76BACE1B-BDCC-F34F-9205-7BB42BE8027F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="47160" windowHeight="21580" xr2:uid="{76BACE1B-BDCC-F34F-9205-7BB42BE8027F}"/>
   </bookViews>
   <sheets>
     <sheet name="Registry Resources" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="110">
   <si>
     <t>Technology</t>
   </si>
@@ -314,39 +314,9 @@
     <t>Підсистема управління нереляційними базами даних</t>
   </si>
   <si>
-    <t>Service Mesh member</t>
-  </si>
-  <si>
     <t>Java</t>
   </si>
   <si>
-    <t>-Xms</t>
-  </si>
-  <si>
-    <t>-Xmx</t>
-  </si>
-  <si>
-    <t>1536m</t>
-  </si>
-  <si>
-    <t>768m</t>
-  </si>
-  <si>
-    <t>512m</t>
-  </si>
-  <si>
-    <t>1200m</t>
-  </si>
-  <si>
-    <t>128m</t>
-  </si>
-  <si>
-    <t>330m</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -359,13 +329,43 @@
     <t>Zone</t>
   </si>
   <si>
-    <t>Criticality</t>
-  </si>
-  <si>
-    <t>non-critical</t>
-  </si>
-  <si>
-    <t>critical</t>
+    <t>Service Mesh</t>
+  </si>
+  <si>
+    <t>Monitoring</t>
+  </si>
+  <si>
+    <t>Java Opts</t>
+  </si>
+  <si>
+    <t>-XX:+ExplicitGCInvokesConcurrent -XX:+AlwaysPreTouch -XX:+UseG1GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -XX:+AlwaysPreTouch -XX:+UseG1GC</t>
+  </si>
+  <si>
+    <t>-Duser.timezone=UTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -Duser.timezone=UTC</t>
+  </si>
+  <si>
+    <t>-XX:+AlwaysPreTouch -XX:+UseG1GC</t>
+  </si>
+  <si>
+    <t>-Xms, Mb</t>
+  </si>
+  <si>
+    <t>-Xmx, Mb</t>
+  </si>
+  <si>
+    <t>-Xmn, Mb</t>
+  </si>
+  <si>
+    <t>Deployment Mode</t>
+  </si>
+  <si>
+    <t>Min Profile</t>
   </si>
 </sst>
 </file>
@@ -443,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -452,11 +452,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -470,18 +483,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:I65" totalsRowShown="0">
-  <autoFilter ref="A1:I65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:M65" totalsRowShown="0">
+  <autoFilter ref="A1:M65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{7B40E2F0-02D6-904B-8018-66FABFA0DD1D}" name="Zone"/>
     <tableColumn id="2" xr3:uid="{9B6E3613-3147-0A49-A88D-DE5E5756377A}" name="Subsystem"/>
     <tableColumn id="3" xr3:uid="{7B693F86-BB20-4643-8C59-CE9AAFCBF004}" name="Component"/>
     <tableColumn id="4" xr3:uid="{BDC056D6-A828-3747-8D2F-B230006DB630}" name="Type"/>
-    <tableColumn id="9" xr3:uid="{26E395E2-1F19-C84B-980C-08C4B5582553}" name="Criticality"/>
-    <tableColumn id="5" xr3:uid="{E36D12C6-BEC1-3841-BB7F-07B8DD85B728}" name="Service Mesh member"/>
+    <tableColumn id="9" xr3:uid="{26E395E2-1F19-C84B-980C-08C4B5582553}" name="Deployment Mode"/>
+    <tableColumn id="14" xr3:uid="{206BB385-4C22-624D-A2DB-36D434439669}" name="Min Profile" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{E36D12C6-BEC1-3841-BB7F-07B8DD85B728}" name="Service Mesh" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{DE3293B1-99DC-3448-B36C-7DC56C231CB7}" name="Monitoring"/>
     <tableColumn id="6" xr3:uid="{90E59384-34DA-9D4D-8715-BED9DC803BBE}" name="Technology"/>
-    <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms"/>
-    <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx"/>
+    <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms, Mb"/>
+    <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx, Mb"/>
+    <tableColumn id="13" xr3:uid="{729BA2AA-0236-6D4E-88FA-AF5279155852}" name="-Xmn, Mb"/>
+    <tableColumn id="12" xr3:uid="{84FF7781-94A1-1246-98C1-52FEAF154639}" name="Java Opts"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -784,49 +801,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C809D083-7CF6-1445-A306-E810BD791428}">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="65.83203125" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
     <col min="4" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="6" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="L1" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -839,14 +871,14 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -859,14 +891,14 @@
       <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -879,14 +911,14 @@
       <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -899,14 +931,14 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -919,23 +951,29 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -948,14 +986,14 @@
       <c r="D7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>73</v>
       </c>
@@ -968,14 +1006,14 @@
       <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>73</v>
       </c>
@@ -988,14 +1026,14 @@
       <c r="D9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -1008,14 +1046,14 @@
       <c r="D10" t="s">
         <v>15</v>
       </c>
-      <c r="E10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>73</v>
       </c>
@@ -1028,23 +1066,29 @@
       <c r="D11" t="s">
         <v>15</v>
       </c>
-      <c r="E11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>73</v>
       </c>
@@ -1057,14 +1101,29 @@
       <c r="D12" t="s">
         <v>15</v>
       </c>
-      <c r="E12" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -1077,14 +1136,14 @@
       <c r="D13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -1097,14 +1156,14 @@
       <c r="D14" t="s">
         <v>15</v>
       </c>
-      <c r="E14" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F14" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -1117,23 +1176,29 @@
       <c r="D15" t="s">
         <v>15</v>
       </c>
-      <c r="E15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J15" s="6">
+        <v>512</v>
+      </c>
+      <c r="K15" s="6">
+        <v>512</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -1146,14 +1211,29 @@
       <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="E16" t="s">
-        <v>108</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -1166,14 +1246,14 @@
       <c r="D17" t="s">
         <v>15</v>
       </c>
-      <c r="E17" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -1186,14 +1266,14 @@
       <c r="D18" t="s">
         <v>15</v>
       </c>
-      <c r="E18" t="s">
-        <v>109</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1206,14 +1286,14 @@
       <c r="D19" t="s">
         <v>15</v>
       </c>
-      <c r="E19" t="s">
-        <v>109</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F19" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -1226,14 +1306,14 @@
       <c r="D20" t="s">
         <v>15</v>
       </c>
-      <c r="E20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>74</v>
       </c>
@@ -1246,14 +1326,14 @@
       <c r="D21" t="s">
         <v>15</v>
       </c>
-      <c r="E21" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -1266,23 +1346,29 @@
       <c r="D22" t="s">
         <v>15</v>
       </c>
-      <c r="E22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" t="s">
-        <v>93</v>
-      </c>
-      <c r="H22" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="6">
+        <v>1536</v>
+      </c>
+      <c r="K22" s="6">
+        <v>1536</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -1295,20 +1381,29 @@
       <c r="D23" t="s">
         <v>15</v>
       </c>
-      <c r="F23" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" t="s">
-        <v>98</v>
-      </c>
-      <c r="I23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J23" s="6">
+        <v>512</v>
+      </c>
+      <c r="K23" s="6">
+        <v>512</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -1321,23 +1416,29 @@
       <c r="D24" t="s">
         <v>15</v>
       </c>
-      <c r="E24" t="s">
-        <v>109</v>
-      </c>
-      <c r="F24" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" t="s">
-        <v>102</v>
-      </c>
-      <c r="I24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -1350,14 +1451,14 @@
       <c r="D25" t="s">
         <v>15</v>
       </c>
-      <c r="E25" t="s">
-        <v>109</v>
-      </c>
-      <c r="F25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F25" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1370,23 +1471,29 @@
       <c r="D26" t="s">
         <v>15</v>
       </c>
-      <c r="E26" t="s">
-        <v>109</v>
-      </c>
-      <c r="F26" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" t="s">
-        <v>101</v>
-      </c>
-      <c r="I26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F26" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J26" s="6">
+        <v>330</v>
+      </c>
+      <c r="K26" s="6">
+        <v>330</v>
+      </c>
+      <c r="L26" s="6">
+        <v>200</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -1399,23 +1506,29 @@
       <c r="D27" t="s">
         <v>15</v>
       </c>
-      <c r="E27" t="s">
-        <v>109</v>
-      </c>
-      <c r="F27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" t="s">
-        <v>101</v>
-      </c>
-      <c r="I27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F27" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J27" s="6">
+        <v>330</v>
+      </c>
+      <c r="K27" s="6">
+        <v>330</v>
+      </c>
+      <c r="L27" s="6">
+        <v>200</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -1428,23 +1541,29 @@
       <c r="D28" t="s">
         <v>15</v>
       </c>
-      <c r="E28" t="s">
-        <v>109</v>
-      </c>
-      <c r="F28" t="s">
-        <v>3</v>
-      </c>
-      <c r="G28" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" t="s">
-        <v>98</v>
-      </c>
-      <c r="I28" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F28" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J28" s="6">
+        <v>512</v>
+      </c>
+      <c r="K28" s="6">
+        <v>512</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -1457,23 +1576,29 @@
       <c r="D29" t="s">
         <v>15</v>
       </c>
-      <c r="E29" t="s">
-        <v>109</v>
-      </c>
-      <c r="F29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" t="s">
-        <v>93</v>
-      </c>
-      <c r="H29" t="s">
-        <v>98</v>
-      </c>
-      <c r="I29" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F29" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J29" s="6">
+        <v>512</v>
+      </c>
+      <c r="K29" s="6">
+        <v>512</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -1486,23 +1611,29 @@
       <c r="D30" t="s">
         <v>15</v>
       </c>
-      <c r="E30" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30" t="s">
-        <v>3</v>
-      </c>
-      <c r="G30" t="s">
-        <v>93</v>
-      </c>
-      <c r="H30" t="s">
-        <v>99</v>
-      </c>
-      <c r="I30" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F30" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J30" s="6">
+        <v>1200</v>
+      </c>
+      <c r="K30" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1515,23 +1646,29 @@
       <c r="D31" t="s">
         <v>15</v>
       </c>
-      <c r="E31" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" t="s">
-        <v>3</v>
-      </c>
-      <c r="G31" t="s">
-        <v>93</v>
-      </c>
-      <c r="H31" t="s">
-        <v>99</v>
-      </c>
-      <c r="I31" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F31" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J31" s="6">
+        <v>1200</v>
+      </c>
+      <c r="K31" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1544,14 +1681,14 @@
       <c r="D32" t="s">
         <v>15</v>
       </c>
-      <c r="E32" t="s">
-        <v>109</v>
-      </c>
-      <c r="F32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F32" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1564,14 +1701,14 @@
       <c r="D33" t="s">
         <v>2</v>
       </c>
-      <c r="E33" t="s">
-        <v>109</v>
-      </c>
-      <c r="F33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F33" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -1584,14 +1721,14 @@
       <c r="D34" t="s">
         <v>2</v>
       </c>
-      <c r="E34" t="s">
-        <v>109</v>
-      </c>
-      <c r="F34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F34" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -1604,14 +1741,14 @@
       <c r="D35" t="s">
         <v>15</v>
       </c>
-      <c r="E35" t="s">
-        <v>109</v>
-      </c>
-      <c r="F35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1624,14 +1761,14 @@
       <c r="D36" t="s">
         <v>15</v>
       </c>
-      <c r="E36" t="s">
-        <v>109</v>
-      </c>
-      <c r="F36" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F36" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -1644,14 +1781,14 @@
       <c r="D37" t="s">
         <v>15</v>
       </c>
-      <c r="E37" t="s">
-        <v>109</v>
-      </c>
-      <c r="F37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F37" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -1664,23 +1801,29 @@
       <c r="D38" t="s">
         <v>15</v>
       </c>
-      <c r="E38" t="s">
-        <v>109</v>
-      </c>
-      <c r="F38" t="s">
-        <v>3</v>
-      </c>
-      <c r="G38" t="s">
-        <v>93</v>
-      </c>
-      <c r="H38" t="s">
-        <v>98</v>
-      </c>
-      <c r="I38" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F38" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J38" s="6">
+        <v>512</v>
+      </c>
+      <c r="K38" s="6">
+        <v>512</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -1693,23 +1836,29 @@
       <c r="D39" t="s">
         <v>15</v>
       </c>
-      <c r="E39" t="s">
-        <v>109</v>
-      </c>
-      <c r="F39" t="s">
-        <v>3</v>
-      </c>
-      <c r="G39" t="s">
-        <v>93</v>
-      </c>
-      <c r="H39" t="s">
-        <v>101</v>
-      </c>
-      <c r="I39" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F39" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J39" s="6">
+        <v>330</v>
+      </c>
+      <c r="K39" s="6">
+        <v>330</v>
+      </c>
+      <c r="L39" s="6">
+        <v>200</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -1722,23 +1871,29 @@
       <c r="D40" t="s">
         <v>15</v>
       </c>
-      <c r="E40" t="s">
-        <v>109</v>
-      </c>
-      <c r="F40" t="s">
-        <v>3</v>
-      </c>
-      <c r="G40" t="s">
-        <v>93</v>
-      </c>
-      <c r="H40" t="s">
-        <v>99</v>
-      </c>
-      <c r="I40" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J40" s="6">
+        <v>1200</v>
+      </c>
+      <c r="K40" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -1751,23 +1906,29 @@
       <c r="D41" t="s">
         <v>15</v>
       </c>
-      <c r="E41" t="s">
-        <v>109</v>
-      </c>
-      <c r="F41" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" t="s">
-        <v>93</v>
-      </c>
-      <c r="H41" t="s">
-        <v>99</v>
-      </c>
-      <c r="I41" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J41" s="6">
+        <v>1200</v>
+      </c>
+      <c r="K41" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -1780,23 +1941,29 @@
       <c r="D42" t="s">
         <v>15</v>
       </c>
-      <c r="E42" t="s">
-        <v>109</v>
-      </c>
-      <c r="F42" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" t="s">
-        <v>93</v>
-      </c>
-      <c r="H42" t="s">
+      <c r="F42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J42" s="6">
+        <v>128</v>
+      </c>
+      <c r="K42" s="6">
+        <v>128</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M42" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I42" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -1809,14 +1976,29 @@
       <c r="D43" t="s">
         <v>15</v>
       </c>
-      <c r="E43" t="s">
-        <v>108</v>
-      </c>
-      <c r="F43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F43" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>74</v>
       </c>
@@ -1829,23 +2011,29 @@
       <c r="D44" t="s">
         <v>15</v>
       </c>
-      <c r="E44" t="s">
-        <v>109</v>
-      </c>
-      <c r="F44" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H44" t="s">
-        <v>101</v>
-      </c>
-      <c r="I44" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F44" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J44" s="6">
+        <v>330</v>
+      </c>
+      <c r="K44" s="6">
+        <v>330</v>
+      </c>
+      <c r="L44" s="6">
+        <v>200</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>74</v>
       </c>
@@ -1858,23 +2046,29 @@
       <c r="D45" t="s">
         <v>15</v>
       </c>
-      <c r="E45" t="s">
-        <v>109</v>
-      </c>
-      <c r="F45" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" t="s">
-        <v>93</v>
-      </c>
-      <c r="H45" t="s">
+      <c r="F45" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J45" s="6">
+        <v>330</v>
+      </c>
+      <c r="K45" s="6">
+        <v>330</v>
+      </c>
+      <c r="L45" s="6">
+        <v>200</v>
+      </c>
+      <c r="M45" t="s">
         <v>101</v>
       </c>
-      <c r="I45" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -1887,23 +2081,29 @@
       <c r="D46" t="s">
         <v>15</v>
       </c>
-      <c r="E46" t="s">
-        <v>109</v>
-      </c>
-      <c r="F46" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" t="s">
-        <v>93</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="F46" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J46" s="6">
+        <v>330</v>
+      </c>
+      <c r="K46" s="6">
+        <v>330</v>
+      </c>
+      <c r="L46" s="6">
+        <v>200</v>
+      </c>
+      <c r="M46" t="s">
         <v>101</v>
       </c>
-      <c r="I46" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -1916,23 +2116,29 @@
       <c r="D47" t="s">
         <v>15</v>
       </c>
-      <c r="E47" t="s">
-        <v>109</v>
-      </c>
-      <c r="F47" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" t="s">
-        <v>93</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="F47" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J47" s="6">
+        <v>330</v>
+      </c>
+      <c r="K47" s="6">
+        <v>330</v>
+      </c>
+      <c r="L47" s="6">
+        <v>200</v>
+      </c>
+      <c r="M47" t="s">
         <v>101</v>
       </c>
-      <c r="I47" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1945,23 +2151,29 @@
       <c r="D48" t="s">
         <v>15</v>
       </c>
-      <c r="E48" t="s">
-        <v>109</v>
-      </c>
-      <c r="F48" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" t="s">
-        <v>93</v>
-      </c>
-      <c r="H48" t="s">
-        <v>102</v>
-      </c>
-      <c r="I48" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F48" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1974,14 +2186,29 @@
       <c r="D49" t="s">
         <v>15</v>
       </c>
-      <c r="E49" t="s">
-        <v>109</v>
-      </c>
-      <c r="F49" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>74</v>
       </c>
@@ -1994,14 +2221,14 @@
       <c r="D50" t="s">
         <v>15</v>
       </c>
-      <c r="E50" t="s">
-        <v>109</v>
-      </c>
-      <c r="F50" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F50" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>74</v>
       </c>
@@ -2014,14 +2241,14 @@
       <c r="D51" t="s">
         <v>15</v>
       </c>
-      <c r="E51" t="s">
-        <v>109</v>
-      </c>
-      <c r="F51" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F51" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -2034,23 +2261,29 @@
       <c r="D52" t="s">
         <v>15</v>
       </c>
-      <c r="E52" t="s">
-        <v>109</v>
-      </c>
-      <c r="F52" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" t="s">
-        <v>93</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="F52" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J52" s="6">
+        <v>330</v>
+      </c>
+      <c r="K52" s="6">
+        <v>330</v>
+      </c>
+      <c r="L52" s="6">
+        <v>200</v>
+      </c>
+      <c r="M52" t="s">
         <v>101</v>
       </c>
-      <c r="I52" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>74</v>
       </c>
@@ -2063,23 +2296,29 @@
       <c r="D53" t="s">
         <v>15</v>
       </c>
-      <c r="E53" t="s">
-        <v>109</v>
-      </c>
-      <c r="F53" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" t="s">
-        <v>93</v>
-      </c>
-      <c r="H53" t="s">
-        <v>97</v>
+      <c r="F53" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="I53" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+      <c r="J53" s="6">
+        <v>768</v>
+      </c>
+      <c r="K53" s="6">
+        <v>768</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>74</v>
       </c>
@@ -2092,14 +2331,14 @@
       <c r="D54" t="s">
         <v>2</v>
       </c>
-      <c r="E54" t="s">
-        <v>109</v>
-      </c>
-      <c r="F54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F54" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>74</v>
       </c>
@@ -2112,14 +2351,14 @@
       <c r="D55" t="s">
         <v>15</v>
       </c>
-      <c r="E55" t="s">
-        <v>109</v>
-      </c>
-      <c r="F55" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F55" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>74</v>
       </c>
@@ -2132,14 +2371,14 @@
       <c r="D56" t="s">
         <v>15</v>
       </c>
-      <c r="E56" t="s">
-        <v>109</v>
-      </c>
-      <c r="F56" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -2152,14 +2391,14 @@
       <c r="D57" t="s">
         <v>2</v>
       </c>
-      <c r="E57" t="s">
-        <v>109</v>
-      </c>
-      <c r="F57" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F57" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>74</v>
       </c>
@@ -2172,14 +2411,14 @@
       <c r="D58" t="s">
         <v>2</v>
       </c>
-      <c r="E58" t="s">
-        <v>109</v>
-      </c>
-      <c r="F58" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F58" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>74</v>
       </c>
@@ -2192,14 +2431,14 @@
       <c r="D59" t="s">
         <v>15</v>
       </c>
-      <c r="E59" t="s">
-        <v>109</v>
-      </c>
-      <c r="F59" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F59" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -2212,14 +2451,14 @@
       <c r="D60" t="s">
         <v>15</v>
       </c>
-      <c r="E60" t="s">
-        <v>109</v>
-      </c>
-      <c r="F60" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F60" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -2232,14 +2471,14 @@
       <c r="D61" t="s">
         <v>2</v>
       </c>
-      <c r="E61" t="s">
-        <v>109</v>
-      </c>
-      <c r="F61" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F61" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -2252,14 +2491,14 @@
       <c r="D62" t="s">
         <v>2</v>
       </c>
-      <c r="E62" t="s">
-        <v>109</v>
-      </c>
-      <c r="F62" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F62" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -2272,14 +2511,14 @@
       <c r="D63" t="s">
         <v>15</v>
       </c>
-      <c r="E63" t="s">
-        <v>109</v>
-      </c>
-      <c r="F63" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F63" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -2292,14 +2531,14 @@
       <c r="D64" t="s">
         <v>2</v>
       </c>
-      <c r="E64" t="s">
-        <v>109</v>
-      </c>
-      <c r="F64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F64" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -2312,10 +2551,10 @@
       <c r="D65" t="s">
         <v>15</v>
       </c>
-      <c r="E65" t="s">
-        <v>109</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="F65" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G65" s="6" t="s">
         <v>3</v>
       </c>
     </row>

--- a/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
+++ b/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Work/Development/mdtu-ddm/mdtu-ddm-gerrit-workspace/mdtu-ddm/general/ddm-architecture/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D966C3E-2F98-AA4E-8DB0-3BC59D58316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB160AE-88B5-0749-B0EB-1A7B5B2006B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="47160" windowHeight="21580" xr2:uid="{76BACE1B-BDCC-F34F-9205-7BB42BE8027F}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{76BACE1B-BDCC-F34F-9205-7BB42BE8027F}"/>
   </bookViews>
   <sheets>
     <sheet name="Registry Resources" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="114">
   <si>
     <t>Technology</t>
   </si>
@@ -366,6 +366,18 @@
   </si>
   <si>
     <t>Min Profile</t>
+  </si>
+  <si>
+    <t>CPU requests</t>
+  </si>
+  <si>
+    <t>CPU limits</t>
+  </si>
+  <si>
+    <t>Memory requests</t>
+  </si>
+  <si>
+    <t>Memory limits</t>
   </si>
 </sst>
 </file>
@@ -483,9 +495,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:M65" totalsRowShown="0">
-  <autoFilter ref="A1:M65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:Q65" totalsRowShown="0">
+  <autoFilter ref="A1:Q65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}"/>
+  <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{7B40E2F0-02D6-904B-8018-66FABFA0DD1D}" name="Zone"/>
     <tableColumn id="2" xr3:uid="{9B6E3613-3147-0A49-A88D-DE5E5756377A}" name="Subsystem"/>
     <tableColumn id="3" xr3:uid="{7B693F86-BB20-4643-8C59-CE9AAFCBF004}" name="Component"/>
@@ -495,6 +507,10 @@
     <tableColumn id="5" xr3:uid="{E36D12C6-BEC1-3841-BB7F-07B8DD85B728}" name="Service Mesh" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{DE3293B1-99DC-3448-B36C-7DC56C231CB7}" name="Monitoring"/>
     <tableColumn id="6" xr3:uid="{90E59384-34DA-9D4D-8715-BED9DC803BBE}" name="Technology"/>
+    <tableColumn id="10" xr3:uid="{377A7AC7-A184-3C48-8086-D39E59847613}" name="CPU requests"/>
+    <tableColumn id="15" xr3:uid="{A68A20D7-80D6-024B-9175-46DB49055D1E}" name="CPU limits"/>
+    <tableColumn id="16" xr3:uid="{DEBD3593-F949-C44D-9F55-7F38F0A28A4E}" name="Memory requests"/>
+    <tableColumn id="17" xr3:uid="{1196C492-F6F6-074A-B99F-1E8E358E5624}" name="Memory limits"/>
     <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms, Mb"/>
     <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx, Mb"/>
     <tableColumn id="13" xr3:uid="{729BA2AA-0236-6D4E-88FA-AF5279155852}" name="-Xmn, Mb"/>
@@ -801,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C809D083-7CF6-1445-A306-E810BD791428}">
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:Q65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
@@ -812,12 +828,16 @@
     <col min="7" max="7" width="15.5" style="6" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
     <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.5" customWidth="1"/>
-    <col min="11" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="60.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="18.6640625" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="16" width="14.33203125" customWidth="1"/>
+    <col min="17" max="17" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>96</v>
       </c>
@@ -845,20 +865,32 @@
       <c r="I1" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -878,7 +910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -898,7 +930,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -918,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -938,7 +970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -960,20 +992,20 @@
       <c r="I6" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -993,7 +1025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>73</v>
       </c>
@@ -1013,7 +1045,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>73</v>
       </c>
@@ -1033,7 +1065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -1053,7 +1085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>73</v>
       </c>
@@ -1075,20 +1107,20 @@
       <c r="I11" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>73</v>
       </c>
@@ -1110,20 +1142,20 @@
       <c r="I12" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -1143,7 +1175,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -1163,7 +1195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -1185,20 +1217,20 @@
       <c r="I15" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J15" s="6">
+      <c r="N15" s="6">
         <v>512</v>
       </c>
-      <c r="K15" s="6">
+      <c r="O15" s="6">
         <v>512</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="P15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -1220,20 +1252,20 @@
       <c r="I16" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -1253,7 +1285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -1273,7 +1305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1293,7 +1325,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -1313,7 +1345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>74</v>
       </c>
@@ -1333,7 +1365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -1355,20 +1387,20 @@
       <c r="I22" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J22" s="6">
+      <c r="N22" s="6">
         <v>1536</v>
       </c>
-      <c r="K22" s="6">
+      <c r="O22" s="6">
         <v>1536</v>
       </c>
-      <c r="L22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M22" s="5" t="s">
+      <c r="P22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q22" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -1390,20 +1422,20 @@
       <c r="I23" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J23" s="6">
+      <c r="N23" s="6">
         <v>512</v>
       </c>
-      <c r="K23" s="6">
+      <c r="O23" s="6">
         <v>512</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="P23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -1425,20 +1457,20 @@
       <c r="I24" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -1458,7 +1490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1480,20 +1512,20 @@
       <c r="I26" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J26" s="6">
+      <c r="N26" s="6">
         <v>330</v>
       </c>
-      <c r="K26" s="6">
+      <c r="O26" s="6">
         <v>330</v>
       </c>
-      <c r="L26" s="6">
+      <c r="P26" s="6">
         <v>200</v>
       </c>
-      <c r="M26" s="5" t="s">
+      <c r="Q26" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -1515,20 +1547,20 @@
       <c r="I27" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J27" s="6">
+      <c r="N27" s="6">
         <v>330</v>
       </c>
-      <c r="K27" s="6">
+      <c r="O27" s="6">
         <v>330</v>
       </c>
-      <c r="L27" s="6">
+      <c r="P27" s="6">
         <v>200</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="Q27" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -1550,20 +1582,20 @@
       <c r="I28" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J28" s="6">
+      <c r="N28" s="6">
         <v>512</v>
       </c>
-      <c r="K28" s="6">
+      <c r="O28" s="6">
         <v>512</v>
       </c>
-      <c r="L28" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="P28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -1585,20 +1617,20 @@
       <c r="I29" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J29" s="6">
+      <c r="N29" s="6">
         <v>512</v>
       </c>
-      <c r="K29" s="6">
+      <c r="O29" s="6">
         <v>512</v>
       </c>
-      <c r="L29" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="P29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -1620,20 +1652,20 @@
       <c r="I30" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J30" s="6">
+      <c r="N30" s="6">
         <v>1200</v>
       </c>
-      <c r="K30" s="6">
+      <c r="O30" s="6">
         <v>1200</v>
       </c>
-      <c r="L30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M30" s="5" t="s">
+      <c r="P30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q30" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1655,20 +1687,20 @@
       <c r="I31" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J31" s="6">
+      <c r="N31" s="6">
         <v>1200</v>
       </c>
-      <c r="K31" s="6">
+      <c r="O31" s="6">
         <v>1200</v>
       </c>
-      <c r="L31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M31" s="5" t="s">
+      <c r="P31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q31" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>74</v>
       </c>
@@ -1688,7 +1720,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1708,7 +1740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -1728,7 +1760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -1748,7 +1780,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -1768,7 +1800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -1788,7 +1820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -1810,20 +1842,20 @@
       <c r="I38" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J38" s="6">
+      <c r="N38" s="6">
         <v>512</v>
       </c>
-      <c r="K38" s="6">
+      <c r="O38" s="6">
         <v>512</v>
       </c>
-      <c r="L38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="P38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -1845,20 +1877,20 @@
       <c r="I39" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J39" s="6">
+      <c r="N39" s="6">
         <v>330</v>
       </c>
-      <c r="K39" s="6">
+      <c r="O39" s="6">
         <v>330</v>
       </c>
-      <c r="L39" s="6">
+      <c r="P39" s="6">
         <v>200</v>
       </c>
-      <c r="M39" s="5" t="s">
+      <c r="Q39" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -1880,20 +1912,20 @@
       <c r="I40" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J40" s="6">
+      <c r="N40" s="6">
         <v>1200</v>
       </c>
-      <c r="K40" s="6">
+      <c r="O40" s="6">
         <v>1200</v>
       </c>
-      <c r="L40" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M40" s="5" t="s">
+      <c r="P40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q40" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -1915,20 +1947,20 @@
       <c r="I41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J41" s="6">
+      <c r="N41" s="6">
         <v>1200</v>
       </c>
-      <c r="K41" s="6">
+      <c r="O41" s="6">
         <v>1200</v>
       </c>
-      <c r="L41" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M41" s="5" t="s">
+      <c r="P41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q41" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -1950,20 +1982,20 @@
       <c r="I42" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J42" s="6">
+      <c r="N42" s="6">
         <v>128</v>
       </c>
-      <c r="K42" s="6">
+      <c r="O42" s="6">
         <v>128</v>
       </c>
-      <c r="L42" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M42" s="5" t="s">
+      <c r="P42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -1985,20 +2017,20 @@
       <c r="I43" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>74</v>
       </c>
@@ -2020,20 +2052,20 @@
       <c r="I44" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J44" s="6">
+      <c r="N44" s="6">
         <v>330</v>
       </c>
-      <c r="K44" s="6">
+      <c r="O44" s="6">
         <v>330</v>
       </c>
-      <c r="L44" s="6">
+      <c r="P44" s="6">
         <v>200</v>
       </c>
-      <c r="M44" s="5" t="s">
+      <c r="Q44" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>74</v>
       </c>
@@ -2055,20 +2087,20 @@
       <c r="I45" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J45" s="6">
+      <c r="N45" s="6">
         <v>330</v>
       </c>
-      <c r="K45" s="6">
+      <c r="O45" s="6">
         <v>330</v>
       </c>
-      <c r="L45" s="6">
+      <c r="P45" s="6">
         <v>200</v>
       </c>
-      <c r="M45" t="s">
+      <c r="Q45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2090,20 +2122,20 @@
       <c r="I46" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J46" s="6">
+      <c r="N46" s="6">
         <v>330</v>
       </c>
-      <c r="K46" s="6">
+      <c r="O46" s="6">
         <v>330</v>
       </c>
-      <c r="L46" s="6">
+      <c r="P46" s="6">
         <v>200</v>
       </c>
-      <c r="M46" t="s">
+      <c r="Q46" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -2125,20 +2157,20 @@
       <c r="I47" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J47" s="6">
+      <c r="N47" s="6">
         <v>330</v>
       </c>
-      <c r="K47" s="6">
+      <c r="O47" s="6">
         <v>330</v>
       </c>
-      <c r="L47" s="6">
+      <c r="P47" s="6">
         <v>200</v>
       </c>
-      <c r="M47" t="s">
+      <c r="Q47" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -2160,20 +2192,20 @@
       <c r="I48" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J48" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -2195,20 +2227,20 @@
       <c r="I49" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J49" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K49" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M49" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>74</v>
       </c>
@@ -2228,7 +2260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>74</v>
       </c>
@@ -2248,7 +2280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -2270,20 +2302,20 @@
       <c r="I52" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J52" s="6">
+      <c r="N52" s="6">
         <v>330</v>
       </c>
-      <c r="K52" s="6">
+      <c r="O52" s="6">
         <v>330</v>
       </c>
-      <c r="L52" s="6">
+      <c r="P52" s="6">
         <v>200</v>
       </c>
-      <c r="M52" t="s">
+      <c r="Q52" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>74</v>
       </c>
@@ -2302,23 +2334,23 @@
       <c r="G53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I53" t="s">
-        <v>92</v>
-      </c>
-      <c r="J53" s="6">
+      <c r="I53" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="N53" s="6">
         <v>768</v>
       </c>
-      <c r="K53" s="6">
+      <c r="O53" s="6">
         <v>768</v>
       </c>
-      <c r="L53" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M53" t="s">
+      <c r="P53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q53" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>74</v>
       </c>
@@ -2338,7 +2370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>74</v>
       </c>
@@ -2358,7 +2390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>74</v>
       </c>
@@ -2378,7 +2410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>74</v>
       </c>
@@ -2398,7 +2430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>74</v>
       </c>
@@ -2418,7 +2450,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>74</v>
       </c>
@@ -2438,7 +2470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>74</v>
       </c>
@@ -2458,7 +2490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -2478,7 +2510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -2498,7 +2530,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -2518,7 +2550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>74</v>
       </c>

--- a/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
+++ b/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Work/Development/mdtu-ddm/mdtu-ddm-gerrit-workspace/mdtu-ddm/general/ddm-architecture/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB160AE-88B5-0749-B0EB-1A7B5B2006B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F11191-9170-5349-B930-C450B5863261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{76BACE1B-BDCC-F34F-9205-7BB42BE8027F}"/>
   </bookViews>

--- a/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
+++ b/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Work/Development/mdtu-ddm/mdtu-ddm-gerrit-workspace/mdtu-ddm/general/ddm-architecture/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F11191-9170-5349-B930-C450B5863261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D081CA6-53FB-ED4B-BE1F-5F70907FD489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{76BACE1B-BDCC-F34F-9205-7BB42BE8027F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="115">
   <si>
     <t>Technology</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>Memory limits</t>
+  </si>
+  <si>
+    <t>-XX:+ExplicitGCInvokesConcurrent -XX:G1HeapRegionSize=16M -XX:InitiatingHeapOccupancyPercent=35 -XX:MaxGCPauseMillis=20 -XX:MaxMetaspaceFreeRatio=80 -XX:MetaspaceSize=96m -XX:MinMetaspaceFreeRatio=50 -XX:+UseG1GC</t>
   </si>
 </sst>
 </file>
@@ -455,14 +458,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -470,16 +467,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="18">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -495,26 +564,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:Q65" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:Q65" totalsRowShown="0" dataDxfId="10">
   <autoFilter ref="A1:Q65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{7B40E2F0-02D6-904B-8018-66FABFA0DD1D}" name="Zone"/>
-    <tableColumn id="2" xr3:uid="{9B6E3613-3147-0A49-A88D-DE5E5756377A}" name="Subsystem"/>
-    <tableColumn id="3" xr3:uid="{7B693F86-BB20-4643-8C59-CE9AAFCBF004}" name="Component"/>
-    <tableColumn id="4" xr3:uid="{BDC056D6-A828-3747-8D2F-B230006DB630}" name="Type"/>
-    <tableColumn id="9" xr3:uid="{26E395E2-1F19-C84B-980C-08C4B5582553}" name="Deployment Mode"/>
-    <tableColumn id="14" xr3:uid="{206BB385-4C22-624D-A2DB-36D434439669}" name="Min Profile" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{E36D12C6-BEC1-3841-BB7F-07B8DD85B728}" name="Service Mesh" dataDxfId="0"/>
-    <tableColumn id="11" xr3:uid="{DE3293B1-99DC-3448-B36C-7DC56C231CB7}" name="Monitoring"/>
-    <tableColumn id="6" xr3:uid="{90E59384-34DA-9D4D-8715-BED9DC803BBE}" name="Technology"/>
-    <tableColumn id="10" xr3:uid="{377A7AC7-A184-3C48-8086-D39E59847613}" name="CPU requests"/>
-    <tableColumn id="15" xr3:uid="{A68A20D7-80D6-024B-9175-46DB49055D1E}" name="CPU limits"/>
-    <tableColumn id="16" xr3:uid="{DEBD3593-F949-C44D-9F55-7F38F0A28A4E}" name="Memory requests"/>
-    <tableColumn id="17" xr3:uid="{1196C492-F6F6-074A-B99F-1E8E358E5624}" name="Memory limits"/>
-    <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms, Mb"/>
-    <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx, Mb"/>
-    <tableColumn id="13" xr3:uid="{729BA2AA-0236-6D4E-88FA-AF5279155852}" name="-Xmn, Mb"/>
-    <tableColumn id="12" xr3:uid="{84FF7781-94A1-1246-98C1-52FEAF154639}" name="Java Opts"/>
+    <tableColumn id="1" xr3:uid="{7B40E2F0-02D6-904B-8018-66FABFA0DD1D}" name="Zone" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{9B6E3613-3147-0A49-A88D-DE5E5756377A}" name="Subsystem" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{7B693F86-BB20-4643-8C59-CE9AAFCBF004}" name="Component" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{BDC056D6-A828-3747-8D2F-B230006DB630}" name="Type" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{26E395E2-1F19-C84B-980C-08C4B5582553}" name="Deployment Mode" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{206BB385-4C22-624D-A2DB-36D434439669}" name="Min Profile" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{E36D12C6-BEC1-3841-BB7F-07B8DD85B728}" name="Service Mesh" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{DE3293B1-99DC-3448-B36C-7DC56C231CB7}" name="Monitoring" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{90E59384-34DA-9D4D-8715-BED9DC803BBE}" name="Technology" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{377A7AC7-A184-3C48-8086-D39E59847613}" name="CPU requests" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{A68A20D7-80D6-024B-9175-46DB49055D1E}" name="CPU limits" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{DEBD3593-F949-C44D-9F55-7F38F0A28A4E}" name="Memory requests" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{1196C492-F6F6-074A-B99F-1E8E358E5624}" name="Memory limits" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms, Mb" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx, Mb" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{729BA2AA-0236-6D4E-88FA-AF5279155852}" name="-Xmn, Mb" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{84FF7781-94A1-1246-98C1-52FEAF154639}" name="Java Opts" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -824,17 +893,17 @@
     <col min="2" max="2" width="65.83203125" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
     <col min="4" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="15.5" style="6" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21" style="2" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" style="2" customWidth="1"/>
     <col min="14" max="14" width="13.5" customWidth="1"/>
     <col min="15" max="16" width="14.33203125" customWidth="1"/>
-    <col min="17" max="17" width="60.6640625" customWidth="1"/>
+    <col min="17" max="17" width="65.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
@@ -853,37 +922,37 @@
       <c r="E1" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>97</v>
       </c>
       <c r="H1" t="s">
         <v>98</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="1" t="s">
         <v>107</v>
       </c>
       <c r="Q1" t="s">
@@ -891,107 +960,157 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="4"/>
     </row>
     <row r="3" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="4"/>
     </row>
     <row r="5" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="4"/>
     </row>
     <row r="6" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H6" s="4"/>
       <c r="I6" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
       <c r="N6" s="6" t="s">
         <v>9</v>
       </c>
@@ -1001,112 +1120,162 @@
       <c r="P6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="Q6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="4"/>
     </row>
     <row r="8" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="4"/>
     </row>
     <row r="9" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
+      <c r="D9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="4"/>
     </row>
     <row r="11" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4"/>
       <c r="F11" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H11" s="4"/>
       <c r="I11" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
       <c r="N11" s="6" t="s">
         <v>9</v>
       </c>
@@ -1116,32 +1285,38 @@
       <c r="P11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="Q11" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H12" s="4"/>
       <c r="I12" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
       <c r="N12" s="6" t="s">
         <v>9</v>
       </c>
@@ -1151,72 +1326,100 @@
       <c r="P12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="Q12" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
+      <c r="D13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="4"/>
       <c r="F13" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="4"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
+      <c r="D14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="4"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
+      <c r="D15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="4"/>
       <c r="F15" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H15" s="4"/>
       <c r="I15" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
       <c r="N15" s="6">
         <v>512</v>
       </c>
@@ -1226,32 +1429,38 @@
       <c r="P15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="Q15" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
+      <c r="D16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H16" s="4"/>
       <c r="I16" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
       <c r="N16" s="6" t="s">
         <v>9</v>
       </c>
@@ -1261,132 +1470,193 @@
       <c r="P16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="Q16" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
+      <c r="D17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="4"/>
       <c r="F17" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="4"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="A18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
+      <c r="D18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="4"/>
       <c r="F18" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="4"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="A19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
+      <c r="D19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="4"/>
       <c r="F19" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="4"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="A20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
+      <c r="D20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4"/>
       <c r="F20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="A21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
+      <c r="D21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="4"/>
       <c r="F21" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="A22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
+      <c r="D22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="4"/>
       <c r="F22" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H22" s="4"/>
       <c r="I22" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
       <c r="N22" s="6">
         <v>1536</v>
       </c>
@@ -1396,32 +1666,38 @@
       <c r="P22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q22" s="5" t="s">
+      <c r="Q22" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="A23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
+      <c r="D23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="4"/>
       <c r="F23" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H23" s="4"/>
       <c r="I23" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
       <c r="N23" s="6">
         <v>512</v>
       </c>
@@ -1431,32 +1707,38 @@
       <c r="P23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="Q23" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="A24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
+      <c r="D24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="4"/>
       <c r="F24" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H24" s="4"/>
       <c r="I24" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
       <c r="N24" s="6" t="s">
         <v>9</v>
       </c>
@@ -1466,52 +1748,69 @@
       <c r="P24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="Q24" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="A25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
+      <c r="D25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="4"/>
       <c r="F25" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="4"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="A26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
+      <c r="D26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="4"/>
       <c r="F26" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H26" s="4"/>
       <c r="I26" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
       <c r="N26" s="6">
         <v>330</v>
       </c>
@@ -1521,32 +1820,38 @@
       <c r="P26" s="6">
         <v>200</v>
       </c>
-      <c r="Q26" s="5" t="s">
+      <c r="Q26" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="A27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D27" t="s">
-        <v>15</v>
-      </c>
+      <c r="D27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="4"/>
       <c r="F27" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H27" s="4"/>
       <c r="I27" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
       <c r="N27" s="6">
         <v>330</v>
       </c>
@@ -1556,32 +1861,38 @@
       <c r="P27" s="6">
         <v>200</v>
       </c>
-      <c r="Q27" s="5" t="s">
+      <c r="Q27" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="A28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
+      <c r="D28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="4"/>
       <c r="F28" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H28" s="4"/>
       <c r="I28" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
       <c r="N28" s="6">
         <v>512</v>
       </c>
@@ -1591,32 +1902,38 @@
       <c r="P28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="Q28" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="A29" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D29" t="s">
-        <v>15</v>
-      </c>
+      <c r="D29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="4"/>
       <c r="F29" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H29" s="4"/>
       <c r="I29" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
       <c r="N29" s="6">
         <v>512</v>
       </c>
@@ -1626,32 +1943,38 @@
       <c r="P29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="Q29" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="A30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
+      <c r="D30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="4"/>
       <c r="F30" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H30" s="4"/>
       <c r="I30" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
       <c r="N30" s="6">
         <v>1200</v>
       </c>
@@ -1661,32 +1984,38 @@
       <c r="P30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q30" s="5" t="s">
+      <c r="Q30" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="A31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D31" t="s">
-        <v>15</v>
-      </c>
+      <c r="D31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="4"/>
       <c r="F31" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H31" s="4"/>
       <c r="I31" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
       <c r="N31" s="6">
         <v>1200</v>
       </c>
@@ -1696,152 +2025,224 @@
       <c r="P31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q31" s="5" t="s">
+      <c r="Q31" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="A32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D32" t="s">
-        <v>15</v>
-      </c>
+      <c r="D32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="4"/>
       <c r="F32" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="4"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="A33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E33" s="4"/>
       <c r="F33" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="4"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="A34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E34" s="4"/>
       <c r="F34" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H34" s="4"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="4"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="A35" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D35" t="s">
-        <v>15</v>
-      </c>
+      <c r="D35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="4"/>
       <c r="F35" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="4"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="A36" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D36" t="s">
-        <v>15</v>
-      </c>
+      <c r="D36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="4"/>
       <c r="F36" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H36" s="4"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="4"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="A37" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D37" t="s">
-        <v>15</v>
-      </c>
+      <c r="D37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="4"/>
       <c r="F37" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="4"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="A38" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D38" t="s">
-        <v>15</v>
-      </c>
+      <c r="D38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="4"/>
       <c r="F38" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H38" s="4"/>
       <c r="I38" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
       <c r="N38" s="6">
         <v>512</v>
       </c>
@@ -1851,32 +2252,38 @@
       <c r="P38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="Q38" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>74</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="A39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D39" t="s">
-        <v>15</v>
-      </c>
+      <c r="D39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="4"/>
       <c r="F39" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H39" s="4"/>
       <c r="I39" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
       <c r="N39" s="6">
         <v>330</v>
       </c>
@@ -1886,32 +2293,38 @@
       <c r="P39" s="6">
         <v>200</v>
       </c>
-      <c r="Q39" s="5" t="s">
+      <c r="Q39" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>74</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="A40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D40" t="s">
-        <v>15</v>
-      </c>
+      <c r="D40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="4"/>
       <c r="F40" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H40" s="4"/>
       <c r="I40" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
       <c r="N40" s="6">
         <v>1200</v>
       </c>
@@ -1921,32 +2334,38 @@
       <c r="P40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q40" s="5" t="s">
+      <c r="Q40" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>74</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="A41" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D41" t="s">
-        <v>15</v>
-      </c>
+      <c r="D41" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="4"/>
       <c r="F41" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H41" s="4"/>
       <c r="I41" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
       <c r="N41" s="6">
         <v>1200</v>
       </c>
@@ -1956,32 +2375,38 @@
       <c r="P41" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q41" s="5" t="s">
+      <c r="Q41" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>74</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="A42" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D42" t="s">
-        <v>15</v>
-      </c>
+      <c r="D42" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="4"/>
       <c r="F42" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H42" s="4"/>
       <c r="I42" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
       <c r="N42" s="6">
         <v>128</v>
       </c>
@@ -1991,32 +2416,38 @@
       <c r="P42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q42" s="5" t="s">
+      <c r="Q42" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>74</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="A43" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D43" t="s">
-        <v>15</v>
-      </c>
+      <c r="D43" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="4"/>
       <c r="F43" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H43" s="4"/>
       <c r="I43" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
       <c r="N43" s="6" t="s">
         <v>9</v>
       </c>
@@ -2026,32 +2457,38 @@
       <c r="P43" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="Q43" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>74</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="A44" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D44" t="s">
-        <v>15</v>
-      </c>
+      <c r="D44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="4"/>
       <c r="F44" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H44" s="4"/>
       <c r="I44" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
       <c r="N44" s="6">
         <v>330</v>
       </c>
@@ -2061,32 +2498,38 @@
       <c r="P44" s="6">
         <v>200</v>
       </c>
-      <c r="Q44" s="5" t="s">
+      <c r="Q44" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="A45" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D45" t="s">
-        <v>15</v>
-      </c>
+      <c r="D45" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="4"/>
       <c r="F45" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H45" s="4"/>
       <c r="I45" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
       <c r="N45" s="6">
         <v>330</v>
       </c>
@@ -2096,32 +2539,38 @@
       <c r="P45" s="6">
         <v>200</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="Q45" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>74</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="A46" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D46" t="s">
-        <v>15</v>
-      </c>
+      <c r="D46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="4"/>
       <c r="F46" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H46" s="4"/>
       <c r="I46" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
       <c r="N46" s="6">
         <v>330</v>
       </c>
@@ -2131,32 +2580,38 @@
       <c r="P46" s="6">
         <v>200</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="Q46" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>74</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="A47" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D47" t="s">
-        <v>15</v>
-      </c>
+      <c r="D47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="4"/>
       <c r="F47" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H47" s="4"/>
       <c r="I47" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
       <c r="N47" s="6">
         <v>330</v>
       </c>
@@ -2166,32 +2621,38 @@
       <c r="P47" s="6">
         <v>200</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="Q47" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>74</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="A48" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D48" t="s">
-        <v>15</v>
-      </c>
+      <c r="D48" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="4"/>
       <c r="F48" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H48" s="4"/>
       <c r="I48" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
       <c r="N48" s="6" t="s">
         <v>9</v>
       </c>
@@ -2201,32 +2662,38 @@
       <c r="P48" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="Q48" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>74</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="A49" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D49" t="s">
-        <v>15</v>
-      </c>
+      <c r="D49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="4"/>
       <c r="F49" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H49" s="4"/>
       <c r="I49" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
       <c r="N49" s="6" t="s">
         <v>9</v>
       </c>
@@ -2236,72 +2703,100 @@
       <c r="P49" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="Q49" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="A50" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D50" t="s">
-        <v>15</v>
-      </c>
+      <c r="D50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="4"/>
       <c r="F50" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="6"/>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="4"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>74</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="A51" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D51" t="s">
-        <v>15</v>
-      </c>
+      <c r="D51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="4"/>
       <c r="F51" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H51" s="4"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="4"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>74</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="A52" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D52" t="s">
-        <v>15</v>
-      </c>
+      <c r="D52" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="4"/>
       <c r="F52" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H52" s="4"/>
       <c r="I52" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
       <c r="N52" s="6">
         <v>330</v>
       </c>
@@ -2311,32 +2806,38 @@
       <c r="P52" s="6">
         <v>200</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="Q52" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="A53" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D53" t="s">
-        <v>15</v>
-      </c>
+      <c r="D53" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="4"/>
       <c r="F53" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H53" s="4"/>
       <c r="I53" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
       <c r="N53" s="6">
         <v>768</v>
       </c>
@@ -2346,249 +2847,387 @@
       <c r="P53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="Q53" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>74</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="A54" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E54" s="4"/>
       <c r="F54" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H54" s="4"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="6"/>
+      <c r="P54" s="6"/>
+      <c r="Q54" s="4"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="A55" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D55" t="s">
-        <v>15</v>
-      </c>
+      <c r="D55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="4"/>
       <c r="F55" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H55" s="4"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="4"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>74</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="A56" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D56" t="s">
-        <v>15</v>
-      </c>
+      <c r="D56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="4"/>
       <c r="F56" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>74</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="H56" s="4"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="4"/>
+    </row>
+    <row r="57" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E57" s="4"/>
       <c r="F57" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H57" s="4"/>
+      <c r="I57" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="10" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>74</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="A58" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E58" s="4"/>
       <c r="F58" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H58" s="4"/>
+      <c r="I58" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="4"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>74</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="A59" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D59" t="s">
-        <v>15</v>
-      </c>
+      <c r="D59" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="4"/>
       <c r="F59" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="4"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>74</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="A60" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D60" t="s">
-        <v>15</v>
-      </c>
+      <c r="D60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="4"/>
       <c r="F60" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H60" s="4"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="4"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="A61" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E61" s="4"/>
       <c r="F61" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H61" s="4"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="4"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="A62" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E62" s="4"/>
       <c r="F62" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H62" s="4"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="4"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>74</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="A63" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D63" t="s">
-        <v>15</v>
-      </c>
+      <c r="D63" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="4"/>
       <c r="F63" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="H63" s="4"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="4"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>74</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="A64" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="E64" s="4"/>
       <c r="F64" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>74</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="H64" s="4"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="4"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D65" t="s">
-        <v>15</v>
-      </c>
+      <c r="D65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="4"/>
       <c r="F65" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="H65" s="4"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
+++ b/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Work/Development/mdtu-ddm/mdtu-ddm-gerrit-workspace/mdtu-ddm/general/ddm-architecture/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D081CA6-53FB-ED4B-BE1F-5F70907FD489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EBFF71-DCC4-7A40-A930-0A96D00DC897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{76BACE1B-BDCC-F34F-9205-7BB42BE8027F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="122">
   <si>
     <t>Technology</t>
   </si>
@@ -381,13 +381,34 @@
   </si>
   <si>
     <t>-XX:+ExplicitGCInvokesConcurrent -XX:G1HeapRegionSize=16M -XX:InitiatingHeapOccupancyPercent=35 -XX:MaxGCPauseMillis=20 -XX:MaxMetaspaceFreeRatio=80 -XX:MetaspaceSize=96m -XX:MinMetaspaceFreeRatio=50 -XX:+UseG1GC</t>
+  </si>
+  <si>
+    <t>do not set</t>
+  </si>
+  <si>
+    <t>need to set</t>
+  </si>
+  <si>
+    <t>=-Xmx + 25%</t>
+  </si>
+  <si>
+    <t>=requests(memory)</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>New Java Opts</t>
+  </si>
+  <si>
+    <t>-XX:+UseG1GC -XX:+ExplicitGCInvokesConcurrent -Duser.timezone=UTC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -398,6 +419,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -458,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -491,11 +519,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -507,6 +559,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -524,16 +579,10 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -564,9 +613,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:Q65" totalsRowShown="0" dataDxfId="10">
-  <autoFilter ref="A1:Q65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}"/>
-  <tableColumns count="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:R65" totalsRowShown="0" dataDxfId="18">
+  <autoFilter ref="A1:R65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}"/>
+  <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{7B40E2F0-02D6-904B-8018-66FABFA0DD1D}" name="Zone" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{9B6E3613-3147-0A49-A88D-DE5E5756377A}" name="Subsystem" dataDxfId="16"/>
     <tableColumn id="3" xr3:uid="{7B693F86-BB20-4643-8C59-CE9AAFCBF004}" name="Component" dataDxfId="15"/>
@@ -574,16 +623,17 @@
     <tableColumn id="9" xr3:uid="{26E395E2-1F19-C84B-980C-08C4B5582553}" name="Deployment Mode" dataDxfId="13"/>
     <tableColumn id="14" xr3:uid="{206BB385-4C22-624D-A2DB-36D434439669}" name="Min Profile" dataDxfId="12"/>
     <tableColumn id="5" xr3:uid="{E36D12C6-BEC1-3841-BB7F-07B8DD85B728}" name="Service Mesh" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{DE3293B1-99DC-3448-B36C-7DC56C231CB7}" name="Monitoring" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{90E59384-34DA-9D4D-8715-BED9DC803BBE}" name="Technology" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{377A7AC7-A184-3C48-8086-D39E59847613}" name="CPU requests" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{A68A20D7-80D6-024B-9175-46DB49055D1E}" name="CPU limits" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{DE3293B1-99DC-3448-B36C-7DC56C231CB7}" name="Monitoring" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{90E59384-34DA-9D4D-8715-BED9DC803BBE}" name="Technology" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{377A7AC7-A184-3C48-8086-D39E59847613}" name="CPU requests" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{A68A20D7-80D6-024B-9175-46DB49055D1E}" name="CPU limits" dataDxfId="7"/>
     <tableColumn id="16" xr3:uid="{DEBD3593-F949-C44D-9F55-7F38F0A28A4E}" name="Memory requests" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{1196C492-F6F6-074A-B99F-1E8E358E5624}" name="Memory limits" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms, Mb" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx, Mb" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{729BA2AA-0236-6D4E-88FA-AF5279155852}" name="-Xmn, Mb" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{84FF7781-94A1-1246-98C1-52FEAF154639}" name="Java Opts" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{1196C492-F6F6-074A-B99F-1E8E358E5624}" name="Memory limits" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms, Mb" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx, Mb" dataDxfId="5"/>
+    <tableColumn id="13" xr3:uid="{729BA2AA-0236-6D4E-88FA-AF5279155852}" name="-Xmn, Mb" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{84FF7781-94A1-1246-98C1-52FEAF154639}" name="Java Opts" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{8EF485D1-BA5B-0B42-B711-53E12FB7661E}" name="New Java Opts" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -886,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C809D083-7CF6-1445-A306-E810BD791428}">
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
@@ -904,9 +954,10 @@
     <col min="14" max="14" width="13.5" customWidth="1"/>
     <col min="15" max="16" width="14.33203125" customWidth="1"/>
     <col min="17" max="17" width="65.6640625" customWidth="1"/>
+    <col min="18" max="18" width="66.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>96</v>
       </c>
@@ -958,8 +1009,11 @@
       <c r="Q1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R1" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>73</v>
       </c>
@@ -981,16 +1035,23 @@
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="J2" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
+      <c r="M2" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N2" s="4"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="4"/>
-    </row>
-    <row r="3" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R2" s="6"/>
+    </row>
+    <row r="3" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>73</v>
       </c>
@@ -1012,16 +1073,23 @@
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="J3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="M3" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N3" s="4"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="4"/>
-    </row>
-    <row r="4" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>73</v>
       </c>
@@ -1043,16 +1111,23 @@
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="J4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="M4" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="4"/>
-    </row>
-    <row r="5" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>73</v>
       </c>
@@ -1074,16 +1149,23 @@
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="J5" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="M5" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N5" s="4"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="4"/>
-    </row>
-    <row r="6" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -1107,10 +1189,18 @@
       <c r="I6" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
+      <c r="J6" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N6" s="6" t="s">
         <v>9</v>
       </c>
@@ -1123,8 +1213,11 @@
       <c r="Q6" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R6" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>73</v>
       </c>
@@ -1146,16 +1239,23 @@
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="J7" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
+      <c r="M7" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N7" s="4"/>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="4"/>
-    </row>
-    <row r="8" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R7" s="6"/>
+    </row>
+    <row r="8" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>73</v>
       </c>
@@ -1177,16 +1277,23 @@
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="J8" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="M8" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N8" s="4"/>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="4"/>
-    </row>
-    <row r="9" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R8" s="6"/>
+    </row>
+    <row r="9" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>73</v>
       </c>
@@ -1208,16 +1315,23 @@
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="J9" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="M9" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N9" s="4"/>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="4"/>
-    </row>
-    <row r="10" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R9" s="6"/>
+    </row>
+    <row r="10" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>73</v>
       </c>
@@ -1239,16 +1353,23 @@
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="J10" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
+      <c r="M10" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N10" s="4"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="4"/>
-    </row>
-    <row r="11" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R10" s="6"/>
+    </row>
+    <row r="11" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>73</v>
       </c>
@@ -1272,10 +1393,18 @@
       <c r="I11" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
+      <c r="J11" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N11" s="6" t="s">
         <v>9</v>
       </c>
@@ -1288,8 +1417,11 @@
       <c r="Q11" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>73</v>
       </c>
@@ -1313,10 +1445,18 @@
       <c r="I12" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="J12" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N12" s="6" t="s">
         <v>9</v>
       </c>
@@ -1329,8 +1469,11 @@
       <c r="Q12" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
@@ -1352,16 +1495,23 @@
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="J13" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
+      <c r="M13" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N13" s="4"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="4"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>73</v>
       </c>
@@ -1383,16 +1533,23 @@
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="J14" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
+      <c r="M14" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N14" s="4"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="4"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="6"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>73</v>
       </c>
@@ -1416,10 +1573,18 @@
       <c r="I15" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="J15" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N15" s="6">
         <v>512</v>
       </c>
@@ -1432,8 +1597,11 @@
       <c r="Q15" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>73</v>
       </c>
@@ -1457,10 +1625,18 @@
       <c r="I16" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
+      <c r="J16" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N16" s="6" t="s">
         <v>9</v>
       </c>
@@ -1473,8 +1649,11 @@
       <c r="Q16" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>73</v>
       </c>
@@ -1496,16 +1675,23 @@
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="J17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="M17" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N17" s="4"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
       <c r="Q17" s="4"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="6"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>74</v>
       </c>
@@ -1527,16 +1713,23 @@
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="J18" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
+      <c r="M18" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N18" s="4"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="4"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="6"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>74</v>
       </c>
@@ -1558,16 +1751,23 @@
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="J19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="M19" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N19" s="4"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="4"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="6"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>74</v>
       </c>
@@ -1589,16 +1789,23 @@
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
+      <c r="J20" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="M20" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N20" s="4"/>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
       <c r="Q20" s="4"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="6"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>74</v>
       </c>
@@ -1620,16 +1827,23 @@
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
+      <c r="J21" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="M21" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N21" s="4"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="4"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="6"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>74</v>
       </c>
@@ -1653,10 +1867,18 @@
       <c r="I22" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="J22" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M22" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N22" s="6">
         <v>1536</v>
       </c>
@@ -1669,8 +1891,11 @@
       <c r="Q22" s="8" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>74</v>
       </c>
@@ -1694,10 +1919,18 @@
       <c r="I23" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="J23" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N23" s="6">
         <v>512</v>
       </c>
@@ -1710,8 +1943,11 @@
       <c r="Q23" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>74</v>
       </c>
@@ -1735,10 +1971,18 @@
       <c r="I24" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
+      <c r="J24" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N24" s="6" t="s">
         <v>9</v>
       </c>
@@ -1751,8 +1995,11 @@
       <c r="Q24" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>74</v>
       </c>
@@ -1774,16 +2021,23 @@
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6"/>
+      <c r="J25" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
+      <c r="M25" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N25" s="4"/>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
       <c r="Q25" s="4"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="6"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>74</v>
       </c>
@@ -1807,24 +2061,35 @@
       <c r="I26" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="J26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N26" s="6">
         <v>330</v>
       </c>
       <c r="O26" s="6">
         <v>330</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P26" s="14">
         <v>200</v>
       </c>
-      <c r="Q26" s="8" t="s">
+      <c r="Q26" s="15" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>74</v>
       </c>
@@ -1848,24 +2113,35 @@
       <c r="I27" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
+      <c r="J27" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N27" s="6">
         <v>330</v>
       </c>
       <c r="O27" s="6">
         <v>330</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27" s="14">
         <v>200</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="Q27" s="15" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
@@ -1889,10 +2165,18 @@
       <c r="I28" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
+      <c r="J28" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N28" s="6">
         <v>512</v>
       </c>
@@ -1905,8 +2189,11 @@
       <c r="Q28" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>74</v>
       </c>
@@ -1930,10 +2217,18 @@
       <c r="I29" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
+      <c r="J29" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M29" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N29" s="6">
         <v>512</v>
       </c>
@@ -1946,8 +2241,11 @@
       <c r="Q29" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>74</v>
       </c>
@@ -1971,10 +2269,18 @@
       <c r="I30" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="J30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N30" s="6">
         <v>1200</v>
       </c>
@@ -1984,11 +2290,14 @@
       <c r="P30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="Q30" s="15" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>74</v>
       </c>
@@ -2012,10 +2321,18 @@
       <c r="I31" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
+      <c r="J31" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N31" s="6">
         <v>1200</v>
       </c>
@@ -2025,11 +2342,14 @@
       <c r="P31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q31" s="8" t="s">
+      <c r="Q31" s="15" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2051,16 +2371,23 @@
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
+      <c r="J32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
+      <c r="M32" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N32" s="4"/>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
       <c r="Q32" s="4"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="6"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>74</v>
       </c>
@@ -2082,16 +2409,23 @@
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
+      <c r="J33" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
+      <c r="M33" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N33" s="4"/>
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
       <c r="Q33" s="4"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="6"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>74</v>
       </c>
@@ -2113,16 +2447,23 @@
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
+      <c r="J34" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
+      <c r="M34" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N34" s="4"/>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
       <c r="Q34" s="4"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="6"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>74</v>
       </c>
@@ -2144,16 +2485,23 @@
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
+      <c r="J35" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
+      <c r="M35" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N35" s="4"/>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
       <c r="Q35" s="4"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="6"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>74</v>
       </c>
@@ -2175,16 +2523,23 @@
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="J36" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
+      <c r="M36" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N36" s="4"/>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
       <c r="Q36" s="4"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R36" s="6"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>74</v>
       </c>
@@ -2206,16 +2561,23 @@
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
+      <c r="J37" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
+      <c r="M37" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N37" s="4"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
       <c r="Q37" s="4"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R37" s="6"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>74</v>
       </c>
@@ -2239,10 +2601,18 @@
       <c r="I38" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
+      <c r="J38" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N38" s="6">
         <v>512</v>
       </c>
@@ -2255,8 +2625,11 @@
       <c r="Q38" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>74</v>
       </c>
@@ -2280,24 +2653,35 @@
       <c r="I39" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
+      <c r="J39" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N39" s="6">
         <v>330</v>
       </c>
       <c r="O39" s="6">
         <v>330</v>
       </c>
-      <c r="P39" s="6">
+      <c r="P39" s="14">
         <v>200</v>
       </c>
-      <c r="Q39" s="8" t="s">
+      <c r="Q39" s="15" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>74</v>
       </c>
@@ -2321,10 +2705,18 @@
       <c r="I40" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
+      <c r="J40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N40" s="6">
         <v>1200</v>
       </c>
@@ -2334,11 +2726,14 @@
       <c r="P40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q40" s="8" t="s">
+      <c r="Q40" s="15" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>74</v>
       </c>
@@ -2362,10 +2757,18 @@
       <c r="I41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
+      <c r="J41" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N41" s="6">
         <v>1200</v>
       </c>
@@ -2375,11 +2778,14 @@
       <c r="P41" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q41" s="8" t="s">
+      <c r="Q41" s="15" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>74</v>
       </c>
@@ -2403,10 +2809,18 @@
       <c r="I42" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
+      <c r="J42" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L42" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M42" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N42" s="6">
         <v>128</v>
       </c>
@@ -2416,11 +2830,14 @@
       <c r="P42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Q42" s="8" t="s">
+      <c r="Q42" s="15" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>74</v>
       </c>
@@ -2444,10 +2861,18 @@
       <c r="I43" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
+      <c r="J43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L43" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N43" s="6" t="s">
         <v>9</v>
       </c>
@@ -2460,8 +2885,11 @@
       <c r="Q43" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>74</v>
       </c>
@@ -2485,24 +2913,35 @@
       <c r="I44" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
+      <c r="J44" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M44" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N44" s="6">
         <v>330</v>
       </c>
       <c r="O44" s="6">
         <v>330</v>
       </c>
-      <c r="P44" s="6">
+      <c r="P44" s="14">
         <v>200</v>
       </c>
-      <c r="Q44" s="8" t="s">
+      <c r="Q44" s="15" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>74</v>
       </c>
@@ -2526,24 +2965,35 @@
       <c r="I45" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
+      <c r="J45" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L45" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M45" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N45" s="6">
         <v>330</v>
       </c>
       <c r="O45" s="6">
         <v>330</v>
       </c>
-      <c r="P45" s="6">
+      <c r="P45" s="14">
         <v>200</v>
       </c>
-      <c r="Q45" s="4" t="s">
+      <c r="Q45" s="16" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>74</v>
       </c>
@@ -2567,24 +3017,35 @@
       <c r="I46" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
+      <c r="J46" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L46" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M46" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N46" s="6">
         <v>330</v>
       </c>
       <c r="O46" s="6">
         <v>330</v>
       </c>
-      <c r="P46" s="6">
+      <c r="P46" s="14">
         <v>200</v>
       </c>
-      <c r="Q46" s="4" t="s">
+      <c r="Q46" s="16" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>74</v>
       </c>
@@ -2608,24 +3069,35 @@
       <c r="I47" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
+      <c r="J47" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L47" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M47" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N47" s="6">
         <v>330</v>
       </c>
       <c r="O47" s="6">
         <v>330</v>
       </c>
-      <c r="P47" s="6">
+      <c r="P47" s="14">
         <v>200</v>
       </c>
-      <c r="Q47" s="4" t="s">
+      <c r="Q47" s="16" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>74</v>
       </c>
@@ -2649,10 +3121,18 @@
       <c r="I48" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
+      <c r="J48" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L48" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M48" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N48" s="6" t="s">
         <v>9</v>
       </c>
@@ -2665,8 +3145,11 @@
       <c r="Q48" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>74</v>
       </c>
@@ -2690,10 +3173,18 @@
       <c r="I49" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
+      <c r="J49" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L49" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M49" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N49" s="6" t="s">
         <v>9</v>
       </c>
@@ -2706,8 +3197,11 @@
       <c r="Q49" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>74</v>
       </c>
@@ -2729,16 +3223,23 @@
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
+      <c r="J50" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
+      <c r="M50" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N50" s="4"/>
       <c r="O50" s="6"/>
       <c r="P50" s="6"/>
       <c r="Q50" s="4"/>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="6"/>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>74</v>
       </c>
@@ -2760,16 +3261,23 @@
       </c>
       <c r="H51" s="4"/>
       <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
+      <c r="J51" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
+      <c r="M51" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N51" s="4"/>
       <c r="O51" s="6"/>
       <c r="P51" s="6"/>
       <c r="Q51" s="4"/>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="6"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>74</v>
       </c>
@@ -2793,24 +3301,35 @@
       <c r="I52" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
+      <c r="J52" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L52" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M52" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N52" s="6">
         <v>330</v>
       </c>
       <c r="O52" s="6">
         <v>330</v>
       </c>
-      <c r="P52" s="6">
+      <c r="P52" s="14">
         <v>200</v>
       </c>
-      <c r="Q52" s="4" t="s">
+      <c r="Q52" s="16" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>74</v>
       </c>
@@ -2834,10 +3353,18 @@
       <c r="I53" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
+      <c r="J53" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L53" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M53" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N53" s="6">
         <v>768</v>
       </c>
@@ -2850,8 +3377,11 @@
       <c r="Q53" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>74</v>
       </c>
@@ -2873,16 +3403,23 @@
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
+      <c r="J54" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
+      <c r="M54" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N54" s="4"/>
       <c r="O54" s="6"/>
       <c r="P54" s="6"/>
       <c r="Q54" s="4"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="6"/>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>74</v>
       </c>
@@ -2904,16 +3441,23 @@
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
+      <c r="J55" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
+      <c r="M55" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N55" s="4"/>
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
       <c r="Q55" s="4"/>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="6"/>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>74</v>
       </c>
@@ -2935,16 +3479,23 @@
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
+      <c r="J56" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
+      <c r="M56" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N56" s="4"/>
       <c r="O56" s="6"/>
       <c r="P56" s="6"/>
       <c r="Q56" s="4"/>
-    </row>
-    <row r="57" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+      <c r="R56" s="6"/>
+    </row>
+    <row r="57" spans="1:18" ht="68" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>74</v>
       </c>
@@ -2968,18 +3519,27 @@
       <c r="I57" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
+      <c r="J57" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L57" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M57" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N57" s="6"/>
       <c r="O57" s="6"/>
       <c r="P57" s="6"/>
       <c r="Q57" s="10" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="17"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>74</v>
       </c>
@@ -3003,16 +3563,25 @@
       <c r="I58" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
+      <c r="J58" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L58" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M58" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="N58" s="4"/>
       <c r="O58" s="6"/>
       <c r="P58" s="6"/>
       <c r="Q58" s="4"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="17"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>74</v>
       </c>
@@ -3034,16 +3603,23 @@
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
+      <c r="J59" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
+      <c r="M59" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N59" s="4"/>
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
       <c r="Q59" s="4"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="6"/>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>74</v>
       </c>
@@ -3065,16 +3641,23 @@
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
+      <c r="J60" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
+      <c r="M60" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N60" s="4"/>
       <c r="O60" s="6"/>
       <c r="P60" s="6"/>
       <c r="Q60" s="4"/>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="6"/>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>74</v>
       </c>
@@ -3096,16 +3679,23 @@
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
+      <c r="J61" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
+      <c r="M61" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N61" s="4"/>
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
       <c r="Q61" s="4"/>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="6"/>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>74</v>
       </c>
@@ -3127,16 +3717,23 @@
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
+      <c r="J62" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
+      <c r="M62" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N62" s="4"/>
       <c r="O62" s="6"/>
       <c r="P62" s="6"/>
       <c r="Q62" s="4"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="6"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>74</v>
       </c>
@@ -3158,16 +3755,23 @@
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
+      <c r="J63" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
+      <c r="M63" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N63" s="4"/>
       <c r="O63" s="6"/>
       <c r="P63" s="6"/>
       <c r="Q63" s="4"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="6"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>74</v>
       </c>
@@ -3189,16 +3793,23 @@
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
+      <c r="J64" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
+      <c r="M64" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N64" s="4"/>
       <c r="O64" s="6"/>
       <c r="P64" s="6"/>
       <c r="Q64" s="4"/>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="6"/>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>74</v>
       </c>
@@ -3220,14 +3831,21 @@
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
+      <c r="J65" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>115</v>
+      </c>
       <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
+      <c r="M65" s="13" t="s">
+        <v>118</v>
+      </c>
       <c r="N65" s="4"/>
       <c r="O65" s="6"/>
       <c r="P65" s="6"/>
       <c r="Q65" s="4"/>
+      <c r="R65" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
+++ b/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/registry-resources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Maksym_Kharchenko/Work/Development/mdtu-ddm/mdtu-ddm-gerrit-workspace/mdtu-ddm/general/ddm-architecture/docs/ua/modules/arch/attachments/architecture/platform-system-requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EBFF71-DCC4-7A40-A930-0A96D00DC897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDCEE3C0-E335-7E4D-B62C-27CB95DC80C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{76BACE1B-BDCC-F34F-9205-7BB42BE8027F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="122">
   <si>
     <t>Technology</t>
   </si>
@@ -380,9 +380,6 @@
     <t>Memory limits</t>
   </si>
   <si>
-    <t>-XX:+ExplicitGCInvokesConcurrent -XX:G1HeapRegionSize=16M -XX:InitiatingHeapOccupancyPercent=35 -XX:MaxGCPauseMillis=20 -XX:MaxMetaspaceFreeRatio=80 -XX:MetaspaceSize=96m -XX:MinMetaspaceFreeRatio=50 -XX:+UseG1GC</t>
-  </si>
-  <si>
     <t>do not set</t>
   </si>
   <si>
@@ -402,6 +399,9 @@
   </si>
   <si>
     <t>-XX:+UseG1GC -XX:+ExplicitGCInvokesConcurrent -Duser.timezone=UTC</t>
+  </si>
+  <si>
+    <t>-Xms=256M -XX:+ExplicitGCInvokesConcurrent -XX:G1HeapRegionSize=16M -XX:InitiatingHeapOccupancyPercent=35 -XX:MaxGCPauseMillis=20 -XX:MaxMetaspaceFreeRatio=80 -XX:MetaspaceSize=96m -XX:MinMetaspaceFreeRatio=50 -XX:+UseG1GC</t>
   </si>
 </sst>
 </file>
@@ -546,6 +546,9 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -559,9 +562,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -614,7 +614,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}" name="Table3" displayName="Table3" ref="A1:R65" totalsRowShown="0" dataDxfId="18">
-  <autoFilter ref="A1:R65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}"/>
+  <autoFilter ref="A1:R65" xr:uid="{06C99DE8-B980-0548-85E0-AAF92621FDD9}">
+    <filterColumn colId="8">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{7B40E2F0-02D6-904B-8018-66FABFA0DD1D}" name="Zone" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{9B6E3613-3147-0A49-A88D-DE5E5756377A}" name="Subsystem" dataDxfId="16"/>
@@ -627,12 +633,12 @@
     <tableColumn id="6" xr3:uid="{90E59384-34DA-9D4D-8715-BED9DC803BBE}" name="Technology" dataDxfId="9"/>
     <tableColumn id="10" xr3:uid="{377A7AC7-A184-3C48-8086-D39E59847613}" name="CPU requests" dataDxfId="8"/>
     <tableColumn id="15" xr3:uid="{A68A20D7-80D6-024B-9175-46DB49055D1E}" name="CPU limits" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{DEBD3593-F949-C44D-9F55-7F38F0A28A4E}" name="Memory requests" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{1196C492-F6F6-074A-B99F-1E8E358E5624}" name="Memory limits" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms, Mb" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx, Mb" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{729BA2AA-0236-6D4E-88FA-AF5279155852}" name="-Xmn, Mb" dataDxfId="4"/>
-    <tableColumn id="12" xr3:uid="{84FF7781-94A1-1246-98C1-52FEAF154639}" name="Java Opts" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{DEBD3593-F949-C44D-9F55-7F38F0A28A4E}" name="Memory requests" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{1196C492-F6F6-074A-B99F-1E8E358E5624}" name="Memory limits" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{7D3E02CE-7CDD-5E44-88DF-1162888AE695}" name="-Xms, Mb" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{3D28B649-AB9D-9C49-8889-6B0D4888A8D3}" name="-Xmx, Mb" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{729BA2AA-0236-6D4E-88FA-AF5279155852}" name="-Xmn, Mb" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{84FF7781-94A1-1246-98C1-52FEAF154639}" name="Java Opts" dataDxfId="1"/>
     <tableColumn id="18" xr3:uid="{8EF485D1-BA5B-0B42-B711-53E12FB7661E}" name="New Java Opts" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -942,15 +948,15 @@
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="65.83203125" customWidth="1"/>
     <col min="3" max="3" width="35.5" customWidth="1"/>
-    <col min="4" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21" style="2" customWidth="1"/>
-    <col min="13" max="13" width="21.33203125" style="2" customWidth="1"/>
+    <col min="4" max="5" width="19.6640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="2" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="2" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="21" style="2" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" style="2" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="13.5" customWidth="1"/>
     <col min="15" max="16" width="14.33203125" customWidth="1"/>
     <col min="17" max="17" width="65.6640625" customWidth="1"/>
@@ -1010,10 +1016,10 @@
         <v>99</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>73</v>
       </c>
@@ -1036,14 +1042,14 @@
       <c r="H2" s="4"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N2" s="4"/>
       <c r="O2" s="6"/>
@@ -1051,7 +1057,7 @@
       <c r="Q2" s="4"/>
       <c r="R2" s="6"/>
     </row>
-    <row r="3" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>73</v>
       </c>
@@ -1074,14 +1080,14 @@
       <c r="H3" s="4"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L3" s="6"/>
       <c r="M3" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="6"/>
@@ -1089,7 +1095,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="6"/>
     </row>
-    <row r="4" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>73</v>
       </c>
@@ -1112,14 +1118,14 @@
       <c r="H4" s="4"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
@@ -1127,7 +1133,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="6"/>
     </row>
-    <row r="5" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>73</v>
       </c>
@@ -1150,14 +1156,14 @@
       <c r="H5" s="4"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="6"/>
@@ -1190,22 +1196,22 @@
         <v>92</v>
       </c>
       <c r="J6" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L6" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M6" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="N6" s="14">
+        <v>256</v>
+      </c>
+      <c r="O6" s="14">
+        <v>512</v>
       </c>
       <c r="P6" s="6" t="s">
         <v>9</v>
@@ -1214,10 +1220,10 @@
         <v>9</v>
       </c>
       <c r="R6" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>73</v>
       </c>
@@ -1240,14 +1246,14 @@
       <c r="H7" s="4"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="6"/>
@@ -1255,7 +1261,7 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="6"/>
     </row>
-    <row r="8" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>73</v>
       </c>
@@ -1278,14 +1284,14 @@
       <c r="H8" s="4"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="6"/>
@@ -1293,7 +1299,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>73</v>
       </c>
@@ -1316,14 +1322,14 @@
       <c r="H9" s="4"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="6"/>
@@ -1331,7 +1337,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="6"/>
     </row>
-    <row r="10" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>73</v>
       </c>
@@ -1354,14 +1360,14 @@
       <c r="H10" s="4"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="6"/>
@@ -1394,22 +1400,22 @@
         <v>92</v>
       </c>
       <c r="J11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L11" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M11" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="N11" s="14">
+        <v>512</v>
+      </c>
+      <c r="O11" s="14">
+        <v>1024</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>9</v>
@@ -1418,7 +1424,7 @@
         <v>9</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -1446,22 +1452,22 @@
         <v>92</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L12" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K12" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M12" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="N12" s="14">
+        <v>128</v>
+      </c>
+      <c r="O12" s="14">
+        <v>256</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>9</v>
@@ -1470,10 +1476,10 @@
         <v>9</v>
       </c>
       <c r="R12" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
@@ -1496,14 +1502,14 @@
       <c r="H13" s="4"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L13" s="6"/>
       <c r="M13" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="6"/>
@@ -1511,7 +1517,7 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="6"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>73</v>
       </c>
@@ -1534,14 +1540,14 @@
       <c r="H14" s="4"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="6"/>
@@ -1574,21 +1580,21 @@
         <v>92</v>
       </c>
       <c r="J15" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L15" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M15" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N15" s="6">
+        <v>117</v>
+      </c>
+      <c r="N15" s="14">
         <v>512</v>
       </c>
-      <c r="O15" s="6">
+      <c r="O15" s="14">
         <v>512</v>
       </c>
       <c r="P15" s="6" t="s">
@@ -1598,7 +1604,7 @@
         <v>9</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -1626,22 +1632,22 @@
         <v>92</v>
       </c>
       <c r="J16" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K16" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M16" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="N16" s="14">
+        <v>128</v>
+      </c>
+      <c r="O16" s="14">
+        <v>256</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>9</v>
@@ -1650,10 +1656,10 @@
         <v>9</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>73</v>
       </c>
@@ -1676,14 +1682,14 @@
       <c r="H17" s="4"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L17" s="6"/>
       <c r="M17" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="6"/>
@@ -1691,7 +1697,7 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="6"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>74</v>
       </c>
@@ -1714,14 +1720,14 @@
       <c r="H18" s="4"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="6"/>
@@ -1729,7 +1735,7 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="6"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>74</v>
       </c>
@@ -1752,14 +1758,14 @@
       <c r="H19" s="4"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="6"/>
@@ -1767,7 +1773,7 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="6"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>74</v>
       </c>
@@ -1790,14 +1796,14 @@
       <c r="H20" s="4"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L20" s="6"/>
       <c r="M20" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="6"/>
@@ -1805,7 +1811,7 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="6"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>74</v>
       </c>
@@ -1828,14 +1834,14 @@
       <c r="H21" s="4"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="6"/>
@@ -1868,21 +1874,21 @@
         <v>92</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L22" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M22" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N22" s="6">
+        <v>117</v>
+      </c>
+      <c r="N22" s="14">
         <v>1536</v>
       </c>
-      <c r="O22" s="6">
+      <c r="O22" s="14">
         <v>1536</v>
       </c>
       <c r="P22" s="6" t="s">
@@ -1892,7 +1898,7 @@
         <v>102</v>
       </c>
       <c r="R22" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
@@ -1920,21 +1926,21 @@
         <v>92</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L23" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K23" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M23" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N23" s="6">
+        <v>117</v>
+      </c>
+      <c r="N23" s="14">
         <v>512</v>
       </c>
-      <c r="O23" s="6">
+      <c r="O23" s="14">
         <v>512</v>
       </c>
       <c r="P23" s="6" t="s">
@@ -1944,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="R23" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
@@ -1972,22 +1978,22 @@
         <v>92</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M24" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="N24" s="14">
+        <v>256</v>
+      </c>
+      <c r="O24" s="14">
+        <v>512</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>9</v>
@@ -1996,10 +2002,10 @@
         <v>9</v>
       </c>
       <c r="R24" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>74</v>
       </c>
@@ -2022,14 +2028,14 @@
       <c r="H25" s="4"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N25" s="4"/>
       <c r="O25" s="6"/>
@@ -2062,21 +2068,21 @@
         <v>92</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M26" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N26" s="6">
+        <v>117</v>
+      </c>
+      <c r="N26" s="14">
         <v>330</v>
       </c>
-      <c r="O26" s="6">
+      <c r="O26" s="14">
         <v>330</v>
       </c>
       <c r="P26" s="14">
@@ -2086,7 +2092,7 @@
         <v>104</v>
       </c>
       <c r="R26" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
@@ -2114,21 +2120,21 @@
         <v>92</v>
       </c>
       <c r="J27" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L27" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K27" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M27" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N27" s="6">
+        <v>117</v>
+      </c>
+      <c r="N27" s="14">
         <v>330</v>
       </c>
-      <c r="O27" s="6">
+      <c r="O27" s="14">
         <v>330</v>
       </c>
       <c r="P27" s="14">
@@ -2138,7 +2144,7 @@
         <v>104</v>
       </c>
       <c r="R27" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
@@ -2166,21 +2172,21 @@
         <v>92</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L28" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K28" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M28" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N28" s="6">
+        <v>117</v>
+      </c>
+      <c r="N28" s="14">
         <v>512</v>
       </c>
-      <c r="O28" s="6">
+      <c r="O28" s="14">
         <v>512</v>
       </c>
       <c r="P28" s="6" t="s">
@@ -2190,7 +2196,7 @@
         <v>9</v>
       </c>
       <c r="R28" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
@@ -2218,21 +2224,21 @@
         <v>92</v>
       </c>
       <c r="J29" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L29" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K29" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M29" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N29" s="6">
+        <v>117</v>
+      </c>
+      <c r="N29" s="14">
         <v>512</v>
       </c>
-      <c r="O29" s="6">
+      <c r="O29" s="14">
         <v>512</v>
       </c>
       <c r="P29" s="6" t="s">
@@ -2242,7 +2248,7 @@
         <v>9</v>
       </c>
       <c r="R29" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
@@ -2270,21 +2276,21 @@
         <v>92</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L30" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M30" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N30" s="6">
+        <v>117</v>
+      </c>
+      <c r="N30" s="14">
         <v>1200</v>
       </c>
-      <c r="O30" s="6">
+      <c r="O30" s="14">
         <v>1200</v>
       </c>
       <c r="P30" s="6" t="s">
@@ -2294,7 +2300,7 @@
         <v>100</v>
       </c>
       <c r="R30" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
@@ -2322,21 +2328,21 @@
         <v>92</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L31" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K31" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M31" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N31" s="6">
+        <v>117</v>
+      </c>
+      <c r="N31" s="14">
         <v>1200</v>
       </c>
-      <c r="O31" s="6">
+      <c r="O31" s="14">
         <v>1200</v>
       </c>
       <c r="P31" s="6" t="s">
@@ -2346,10 +2352,10 @@
         <v>100</v>
       </c>
       <c r="R31" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>74</v>
       </c>
@@ -2372,14 +2378,14 @@
       <c r="H32" s="4"/>
       <c r="I32" s="6"/>
       <c r="J32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="6"/>
@@ -2387,7 +2393,7 @@
       <c r="Q32" s="4"/>
       <c r="R32" s="6"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>74</v>
       </c>
@@ -2410,14 +2416,14 @@
       <c r="H33" s="4"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="6"/>
@@ -2425,7 +2431,7 @@
       <c r="Q33" s="4"/>
       <c r="R33" s="6"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>74</v>
       </c>
@@ -2448,14 +2454,14 @@
       <c r="H34" s="4"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L34" s="6"/>
       <c r="M34" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="6"/>
@@ -2463,7 +2469,7 @@
       <c r="Q34" s="4"/>
       <c r="R34" s="6"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>74</v>
       </c>
@@ -2486,14 +2492,14 @@
       <c r="H35" s="4"/>
       <c r="I35" s="6"/>
       <c r="J35" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L35" s="6"/>
       <c r="M35" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="6"/>
@@ -2501,7 +2507,7 @@
       <c r="Q35" s="4"/>
       <c r="R35" s="6"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>74</v>
       </c>
@@ -2524,14 +2530,14 @@
       <c r="H36" s="4"/>
       <c r="I36" s="6"/>
       <c r="J36" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="6"/>
@@ -2539,7 +2545,7 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="6"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>74</v>
       </c>
@@ -2562,14 +2568,14 @@
       <c r="H37" s="4"/>
       <c r="I37" s="6"/>
       <c r="J37" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L37" s="6"/>
       <c r="M37" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="6"/>
@@ -2602,21 +2608,21 @@
         <v>92</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L38" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M38" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N38" s="6">
+        <v>117</v>
+      </c>
+      <c r="N38" s="14">
         <v>512</v>
       </c>
-      <c r="O38" s="6">
+      <c r="O38" s="14">
         <v>512</v>
       </c>
       <c r="P38" s="6" t="s">
@@ -2626,7 +2632,7 @@
         <v>9</v>
       </c>
       <c r="R38" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
@@ -2654,21 +2660,21 @@
         <v>92</v>
       </c>
       <c r="J39" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L39" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K39" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L39" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M39" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N39" s="6">
+        <v>117</v>
+      </c>
+      <c r="N39" s="14">
         <v>330</v>
       </c>
-      <c r="O39" s="6">
+      <c r="O39" s="14">
         <v>330</v>
       </c>
       <c r="P39" s="14">
@@ -2678,7 +2684,7 @@
         <v>104</v>
       </c>
       <c r="R39" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
@@ -2706,21 +2712,21 @@
         <v>92</v>
       </c>
       <c r="J40" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L40" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M40" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N40" s="6">
+        <v>117</v>
+      </c>
+      <c r="N40" s="14">
         <v>1200</v>
       </c>
-      <c r="O40" s="6">
+      <c r="O40" s="14">
         <v>1200</v>
       </c>
       <c r="P40" s="6" t="s">
@@ -2730,7 +2736,7 @@
         <v>100</v>
       </c>
       <c r="R40" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
@@ -2758,21 +2764,21 @@
         <v>92</v>
       </c>
       <c r="J41" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L41" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K41" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L41" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M41" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N41" s="6">
+        <v>117</v>
+      </c>
+      <c r="N41" s="14">
         <v>1200</v>
       </c>
-      <c r="O41" s="6">
+      <c r="O41" s="14">
         <v>1200</v>
       </c>
       <c r="P41" s="6" t="s">
@@ -2782,7 +2788,7 @@
         <v>100</v>
       </c>
       <c r="R41" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
@@ -2810,21 +2816,21 @@
         <v>92</v>
       </c>
       <c r="J42" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L42" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K42" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M42" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N42" s="6">
+        <v>117</v>
+      </c>
+      <c r="N42" s="14">
         <v>128</v>
       </c>
-      <c r="O42" s="6">
+      <c r="O42" s="14">
         <v>128</v>
       </c>
       <c r="P42" s="6" t="s">
@@ -2834,7 +2840,7 @@
         <v>100</v>
       </c>
       <c r="R42" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
@@ -2862,22 +2868,22 @@
         <v>92</v>
       </c>
       <c r="J43" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L43" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K43" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L43" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M43" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="N43" s="14">
+        <v>256</v>
+      </c>
+      <c r="O43" s="14">
+        <v>512</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>9</v>
@@ -2886,7 +2892,7 @@
         <v>9</v>
       </c>
       <c r="R43" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.2">
@@ -2914,21 +2920,21 @@
         <v>92</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L44" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K44" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M44" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N44" s="6">
+        <v>117</v>
+      </c>
+      <c r="N44" s="14">
         <v>330</v>
       </c>
-      <c r="O44" s="6">
+      <c r="O44" s="14">
         <v>330</v>
       </c>
       <c r="P44" s="14">
@@ -2938,7 +2944,7 @@
         <v>104</v>
       </c>
       <c r="R44" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.2">
@@ -2966,21 +2972,21 @@
         <v>92</v>
       </c>
       <c r="J45" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L45" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K45" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L45" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M45" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N45" s="6">
+        <v>117</v>
+      </c>
+      <c r="N45" s="14">
         <v>330</v>
       </c>
-      <c r="O45" s="6">
+      <c r="O45" s="14">
         <v>330</v>
       </c>
       <c r="P45" s="14">
@@ -2990,7 +2996,7 @@
         <v>101</v>
       </c>
       <c r="R45" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
@@ -3018,21 +3024,21 @@
         <v>92</v>
       </c>
       <c r="J46" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L46" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K46" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L46" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M46" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N46" s="6">
+        <v>117</v>
+      </c>
+      <c r="N46" s="14">
         <v>330</v>
       </c>
-      <c r="O46" s="6">
+      <c r="O46" s="14">
         <v>330</v>
       </c>
       <c r="P46" s="14">
@@ -3042,7 +3048,7 @@
         <v>101</v>
       </c>
       <c r="R46" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
@@ -3070,21 +3076,21 @@
         <v>92</v>
       </c>
       <c r="J47" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L47" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K47" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L47" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M47" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N47" s="6">
+        <v>117</v>
+      </c>
+      <c r="N47" s="14">
         <v>330</v>
       </c>
-      <c r="O47" s="6">
+      <c r="O47" s="14">
         <v>330</v>
       </c>
       <c r="P47" s="14">
@@ -3094,7 +3100,7 @@
         <v>101</v>
       </c>
       <c r="R47" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.2">
@@ -3122,22 +3128,22 @@
         <v>92</v>
       </c>
       <c r="J48" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L48" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K48" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L48" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M48" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="N48" s="14">
+        <v>256</v>
+      </c>
+      <c r="O48" s="14">
+        <v>512</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>9</v>
@@ -3146,7 +3152,7 @@
         <v>9</v>
       </c>
       <c r="R48" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
@@ -3174,22 +3180,22 @@
         <v>92</v>
       </c>
       <c r="J49" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L49" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K49" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L49" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M49" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="O49" s="6" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="N49" s="14">
+        <v>256</v>
+      </c>
+      <c r="O49" s="14">
+        <v>512</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>9</v>
@@ -3198,10 +3204,10 @@
         <v>9</v>
       </c>
       <c r="R49" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>74</v>
       </c>
@@ -3224,14 +3230,14 @@
       <c r="H50" s="4"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L50" s="6"/>
       <c r="M50" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="6"/>
@@ -3239,7 +3245,7 @@
       <c r="Q50" s="4"/>
       <c r="R50" s="6"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>74</v>
       </c>
@@ -3262,14 +3268,14 @@
       <c r="H51" s="4"/>
       <c r="I51" s="6"/>
       <c r="J51" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L51" s="6"/>
       <c r="M51" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="6"/>
@@ -3302,21 +3308,21 @@
         <v>92</v>
       </c>
       <c r="J52" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L52" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K52" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L52" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M52" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N52" s="6">
+        <v>117</v>
+      </c>
+      <c r="N52" s="14">
         <v>330</v>
       </c>
-      <c r="O52" s="6">
+      <c r="O52" s="14">
         <v>330</v>
       </c>
       <c r="P52" s="14">
@@ -3326,7 +3332,7 @@
         <v>101</v>
       </c>
       <c r="R52" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
@@ -3354,21 +3360,21 @@
         <v>92</v>
       </c>
       <c r="J53" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="L53" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="K53" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="L53" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="M53" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="N53" s="6">
+        <v>117</v>
+      </c>
+      <c r="N53" s="14">
         <v>768</v>
       </c>
-      <c r="O53" s="6">
+      <c r="O53" s="14">
         <v>768</v>
       </c>
       <c r="P53" s="6" t="s">
@@ -3378,10 +3384,10 @@
         <v>103</v>
       </c>
       <c r="R53" s="17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>74</v>
       </c>
@@ -3404,14 +3410,14 @@
       <c r="H54" s="4"/>
       <c r="I54" s="6"/>
       <c r="J54" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N54" s="4"/>
       <c r="O54" s="6"/>
@@ -3419,7 +3425,7 @@
       <c r="Q54" s="4"/>
       <c r="R54" s="6"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>74</v>
       </c>
@@ -3442,14 +3448,14 @@
       <c r="H55" s="4"/>
       <c r="I55" s="6"/>
       <c r="J55" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L55" s="6"/>
       <c r="M55" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="6"/>
@@ -3457,7 +3463,7 @@
       <c r="Q55" s="4"/>
       <c r="R55" s="6"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>74</v>
       </c>
@@ -3480,14 +3486,14 @@
       <c r="H56" s="4"/>
       <c r="I56" s="6"/>
       <c r="J56" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L56" s="6"/>
       <c r="M56" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N56" s="4"/>
       <c r="O56" s="6"/>
@@ -3520,22 +3526,26 @@
         <v>92</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L57" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M57" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="N57" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
+      <c r="O57" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="P57" s="6"/>
       <c r="Q57" s="10" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="R57" s="17"/>
     </row>
@@ -3564,24 +3574,28 @@
         <v>92</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L58" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M58" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="N58" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="N58" s="4"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="P58" s="6"/>
       <c r="Q58" s="4"/>
       <c r="R58" s="17"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>74</v>
       </c>
@@ -3604,14 +3618,14 @@
       <c r="H59" s="4"/>
       <c r="I59" s="6"/>
       <c r="J59" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L59" s="6"/>
       <c r="M59" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N59" s="4"/>
       <c r="O59" s="6"/>
@@ -3619,7 +3633,7 @@
       <c r="Q59" s="4"/>
       <c r="R59" s="6"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>74</v>
       </c>
@@ -3642,14 +3656,14 @@
       <c r="H60" s="4"/>
       <c r="I60" s="6"/>
       <c r="J60" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L60" s="6"/>
       <c r="M60" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="6"/>
@@ -3657,7 +3671,7 @@
       <c r="Q60" s="4"/>
       <c r="R60" s="6"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>74</v>
       </c>
@@ -3680,14 +3694,14 @@
       <c r="H61" s="4"/>
       <c r="I61" s="6"/>
       <c r="J61" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L61" s="6"/>
       <c r="M61" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N61" s="4"/>
       <c r="O61" s="6"/>
@@ -3695,7 +3709,7 @@
       <c r="Q61" s="4"/>
       <c r="R61" s="6"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>74</v>
       </c>
@@ -3718,14 +3732,14 @@
       <c r="H62" s="4"/>
       <c r="I62" s="6"/>
       <c r="J62" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L62" s="6"/>
       <c r="M62" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N62" s="4"/>
       <c r="O62" s="6"/>
@@ -3733,7 +3747,7 @@
       <c r="Q62" s="4"/>
       <c r="R62" s="6"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>74</v>
       </c>
@@ -3756,14 +3770,14 @@
       <c r="H63" s="4"/>
       <c r="I63" s="6"/>
       <c r="J63" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L63" s="6"/>
       <c r="M63" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N63" s="4"/>
       <c r="O63" s="6"/>
@@ -3771,7 +3785,7 @@
       <c r="Q63" s="4"/>
       <c r="R63" s="6"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>74</v>
       </c>
@@ -3794,14 +3808,14 @@
       <c r="H64" s="4"/>
       <c r="I64" s="6"/>
       <c r="J64" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L64" s="6"/>
       <c r="M64" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="6"/>
@@ -3809,7 +3823,7 @@
       <c r="Q64" s="4"/>
       <c r="R64" s="6"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>74</v>
       </c>
@@ -3832,14 +3846,14 @@
       <c r="H65" s="4"/>
       <c r="I65" s="6"/>
       <c r="J65" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L65" s="6"/>
       <c r="M65" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N65" s="4"/>
       <c r="O65" s="6"/>
